--- a/InFiRA-QA/000732-QA.xlsx
+++ b/InFiRA-QA/000732-QA.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
   <si>
     <t>Question</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,10 +45,177 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
+    <t>请按照合并资产负债表计算流动比率这一年的变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请按照合并资产负债表计算速动比率这一年的变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请按照合并资产负债表计算权益比率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请计算现金比率2022年期初和期末的差额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司董事长是谁？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄其森</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021 年销售费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>境内自然人持股变动后的比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持股最高的股东持股比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有无出售重大资产情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司报告期有无违规对外担保情况？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告期末除债券外的有息债务逾期金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本报告期末流动比率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利息偿付率本报告期比上年同期增减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应交印花税期末余额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账龄超过 1 年的重要其他应付款中合计是多少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021 年度股东大会披露日期是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022 年 05 月 27日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022 年第二次临时股东大会的投资者参与比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余春江的任职状态是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>离任</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是谁被新选上担任监事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阮仕江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司员工中研究生及以上有多少人?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>境内会计师事务所报酬是多少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>450万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司营业收入中2022年零售行业的占比是多少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司主要从事的业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅地产和商业地产的开发及运营</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截至报告期末公司已到期未归还借款金额为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>564.97 亿元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>营业成本构成中按照行业分类占营业成本比重排名第二的是什么行业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物业及酒店管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>营业收入构成中按照行业排名营业收入排名第一的是什么行业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>房地产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请计算该公司2022年的资产报酬率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请计算该公司2022年税前净利润</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照合并利润表计算2022年的销售净利率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归属于母公司所有者权益上年期末盈余公积，在这一年有什么变化？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请计算本报告期末的资产负债率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>−1.48%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少0.27个百分点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
@@ -58,7 +225,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF067D17"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
       </rPr>
@@ -67,7 +233,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF067D17"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
@@ -77,32 +242,81 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>请按照合并资产负债表计算流动比率这一年的变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请按照合并资产负债表计算速动比率这一年的变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请按照合并资产负债表计算权益比率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF080808"/>
+    <r>
+      <t>按照合并利润表对比分析企业</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
+      <t>年期初的核心利润率和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年期末的核心利润率</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>该公司</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年的毛利是多少？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t>请计算</t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF080808"/>
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
@@ -111,7 +325,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF080808"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
@@ -124,7 +337,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF080808"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
@@ -134,7 +346,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF080808"/>
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
@@ -143,7 +354,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF080808"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
@@ -153,240 +363,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>请计算现金比率2022年期初和期末的差额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算上年同期利息保障倍数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算本报告期利息偿付率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司董事长是谁？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄其森</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021 年销售费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>境内自然人持股变动后的比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持股最高的股东持股比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有无出售重大资产情况</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司报告期有无违规对外担保情况？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报告期末除债券外的有息债务逾期金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本报告期末流动比率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>利息偿付率本报告期比上年同期增减</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应交印花税期末余额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>账龄超过 1 年的重要其他应付款中合计是多少</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021 年度股东大会披露日期是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2022 年 05 月 27日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2022 年第二次临时股东大会的投资者参与比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余春江的任职状态是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>离任</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是谁被新选上担任监事</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阮仕江</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司员工中研究生及以上有多少人?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>境内会计师事务所报酬是多少</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>450万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司营业收入中2022年零售行业的占比是多少</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司主要从事的业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>住宅地产和商业地产的开发及运营</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>截至报告期末公司已到期未归还借款金额为</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>564.97 亿元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>营业成本构成中按照行业分类占营业成本比重排名第二的是什么行业</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物业及酒店管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>营业收入构成中按照行业排名营业收入排名第一的是什么行业</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>房地产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算该公司2022年的资产报酬率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>−2.48%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算该公司2022年税前净利润</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>按照合并利润表计算2022年的销售净利率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>归属于母公司所有者权益上年期末盈余公积，在这一年有什么变化？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算本报告期末的资产负债率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算本报告期利息保障倍数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>按照合并利润表对比分析企业</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>2022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年期初的核心利润率和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>2022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年期末的核心利润率</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>该公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
-        <rFont val="JetBrains Mono"/>
-        <family val="3"/>
-      </rPr>
-      <t>2022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF067D17"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年的毛利是多少？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请计算上年同期利息偿付率。利息偿付率=EBIT/利息费用。EBIT（净利润+所得税费用+利息费用）</t>
+    <t>计算该公司的营业利润率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算该公司的总营业费用率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请计算上年同期利息保障倍数（EBIT = 净利润 + 利息费用 ）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请计算本报告期利息保障倍数（EBIT = 净利润 + 利息费用 ）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -394,7 +383,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,42 +399,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF080808"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF067D17"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF067D17"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF080808"/>
-      <name val="宋体"/>
+      <name val="JetBrains Mono"/>
       <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF067D17"/>
-      <name val="等线"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF080808"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -474,13 +447,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -765,14 +737,14 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -781,10 +753,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -792,9 +764,9 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="3">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1">
         <v>481113927.94</v>
       </c>
       <c r="C3" t="s">
@@ -803,9 +775,9 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="C4" t="s">
@@ -814,9 +786,9 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.38229999999999997</v>
       </c>
       <c r="C5" t="s">
@@ -825,9 +797,9 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
@@ -836,9 +808,9 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
@@ -847,9 +819,9 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
         <v>5170872.79</v>
       </c>
       <c r="C8" t="s">
@@ -858,9 +830,9 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="3">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.91859999999999997</v>
       </c>
       <c r="C9" t="s">
@@ -869,9 +841,9 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="C10" t="s">
@@ -880,9 +852,9 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
         <v>406447.32</v>
       </c>
       <c r="C11" t="s">
@@ -891,9 +863,9 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="3">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1">
         <v>4454351771.0200005</v>
       </c>
       <c r="C12" t="s">
@@ -902,10 +874,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -913,9 +885,9 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="5">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3">
         <v>0.42099999999999999</v>
       </c>
       <c r="C14" t="s">
@@ -924,10 +896,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -935,10 +907,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -946,9 +918,9 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="3">
+        <v>29</v>
+      </c>
+      <c r="B17" s="1">
         <v>110</v>
       </c>
       <c r="C17" t="s">
@@ -957,17 +929,17 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5">
+        <v>32</v>
+      </c>
+      <c r="B19" s="3">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="C19" t="s">
@@ -976,10 +948,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -987,10 +959,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -998,10 +970,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -1009,10 +981,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
@@ -1020,10 +992,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
@@ -1031,119 +1003,119 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-3199428804.8299999</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="1">
+        <v>-0.63280000000000003</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15">
+      <c r="A28" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="3">
-        <v>-3199428804.8299999</v>
-      </c>
-      <c r="C25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
+      <c r="B28" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.96079999999999999</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="1">
+        <v>-0.23860000000000001</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15">
+      <c r="A33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="3">
-        <v>-0.63280000000000003</v>
-      </c>
-      <c r="C26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
+      <c r="B33" s="1">
+        <v>0.1173</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15">
+      <c r="A34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="3">
-        <v>0</v>
-      </c>
-      <c r="C27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15">
-      <c r="A28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="3">
-        <v>1.19</v>
-      </c>
-      <c r="C28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3">
-        <v>-0.22559999999999999</v>
-      </c>
-      <c r="C29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+      <c r="B34" s="1">
+        <v>312070066.86000001</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15">
+      <c r="A35" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="3">
-        <v>0.96079999999999999</v>
-      </c>
-      <c r="C30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="3">
-        <v>-0.23860000000000001</v>
-      </c>
-      <c r="C31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="3">
-        <v>3.9199999999999999E-2</v>
-      </c>
-      <c r="C32" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15">
-      <c r="A33" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="3">
-        <v>0.1173</v>
-      </c>
-      <c r="C33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15">
-      <c r="A34" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="3">
-        <v>312070066.86000001</v>
-      </c>
-      <c r="C34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15">
-      <c r="A35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>0.54059999999999997</v>
       </c>
       <c r="C35" t="s">
@@ -1151,10 +1123,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="15">
-      <c r="A36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="3">
+      <c r="A36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="1">
         <v>25.5</v>
       </c>
       <c r="C36" t="s">
@@ -1163,9 +1135,9 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="3">
+        <v>9</v>
+      </c>
+      <c r="B37" s="1">
         <v>-4.2599999999999999E-3</v>
       </c>
       <c r="C37" t="s">
@@ -1174,10 +1146,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="3">
-        <v>-0.37</v>
+        <v>56</v>
+      </c>
+      <c r="B38" s="1">
+        <v>-1.17</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
@@ -1185,10 +1157,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="3">
-        <v>-0.6</v>
+        <v>55</v>
+      </c>
+      <c r="B39" s="1">
+        <v>-0.74</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
@@ -1196,10 +1168,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B40" s="3">
-        <v>9.2299999999999993E-2</v>
+        <v>-0.58809999999999996</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
@@ -1207,10 +1179,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B41" s="3">
-        <v>9.4799999999999995E-2</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
